--- a/online-version.xlsx
+++ b/online-version.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training initiatives" sheetId="1" r:id="R81f2928b47214220"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training initiatives" sheetId="1" r:id="R3b267839a6814368"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -142,17 +142,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrainingInitiativesOnline" displayName="TrainingInitiativesOnline" ref="A3:I34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="9">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrainingInitiativesOnline" displayName="TrainingInitiativesOnline" ref="A3:G34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="7">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Name of Initiative"/>
     <x:tableColumn id="3" name="Region/city"/>
     <x:tableColumn id="4" name="Level"/>
     <x:tableColumn id="5" name="Theme workshop/training"/>
-    <x:tableColumn id="6" name="Challenge or Best Practice"/>
-    <x:tableColumn id="7" name="Notes"/>
-    <x:tableColumn id="8" name="Organisatie"/>
-    <x:tableColumn id="9" name="Links"/>
+    <x:tableColumn id="6" name="Organisatie"/>
+    <x:tableColumn id="7" name="Links"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -357,11 +355,9 @@
     <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="31" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="58" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="58" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -374,12 +370,10 @@
       <x:c r="E1" s="4"/>
       <x:c r="F1" s="4"/>
       <x:c r="G1" s="4"/>
-      <x:c r="H1" s="4"/>
-      <x:c r="I1" s="4"/>
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Contact Details removed for online publication. IDs 19, 20, 21, 26, 33 and 34 are excluded. Entries with incomplete information are retained.</x:v>
+        <x:v>Contact Details, Challenge or Best Practice and Notes removed for online publication. IDs are renumbered sequentially. Entries with incomplete information are retained.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -387,8 +381,6 @@
       <x:c r="E2" s="8"/>
       <x:c r="F2" s="8"/>
       <x:c r="G2" s="8"/>
-      <x:c r="H2" s="8"/>
-      <x:c r="I2" s="8"/>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
       <x:c r="A3" s="11" t="str">
@@ -407,15 +399,9 @@
         <x:v>Theme workshop/training</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>Challenge or Best Practice</x:v>
+        <x:v>Organisatie</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="H3" s="11" t="str">
-        <x:v>Organisatie</x:v>
-      </x:c>
-      <x:c r="I3" s="11" t="str">
         <x:v>Links</x:v>
       </x:c>
     </x:row>
@@ -434,15 +420,9 @@
       </x:c>
       <x:c r="E4" s="18"/>
       <x:c r="F4" s="18" t="str">
-        <x:v>Challenge</x:v>
-      </x:c>
-      <x:c r="G4" s="18" t="str">
-        <x:v>Capacity building in the large national organization</x:v>
-      </x:c>
-      <x:c r="H4" s="18" t="str">
         <x:v>TNO</x:v>
       </x:c>
-      <x:c r="I4" s="18"/>
+      <x:c r="G4" s="18"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="22" t="n">
@@ -461,15 +441,9 @@
         <x:v>HPC Support</x:v>
       </x:c>
       <x:c r="F5" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>Vrije Universiteit Amsterdam</x:v>
       </x:c>
       <x:c r="G5" s="19" t="str">
-        <x:v>Asks for specialist expertise which is scarce. Need for collaboration. Idea: establish a training, traineeship</x:v>
-      </x:c>
-      <x:c r="H5" s="19" t="str">
-        <x:v>Vrije Universiteit Amsterdam</x:v>
-      </x:c>
-      <x:c r="I5" s="19" t="str">
         <x:v>https://vu.nl/en/about-vu/more-about/research-software-support</x:v>
       </x:c>
     </x:row>
@@ -488,15 +462,9 @@
         <x:v>Training researchers in data management</x:v>
       </x:c>
       <x:c r="F6" s="19" t="str">
-        <x:v>Challenge</x:v>
-      </x:c>
-      <x:c r="G6" s="19" t="str">
-        <x:v>Making the session a more practical and hands-on experience</x:v>
-      </x:c>
-      <x:c r="H6" s="19" t="str">
         <x:v>Not determined from Contact Details</x:v>
       </x:c>
-      <x:c r="I6" s="19"/>
+      <x:c r="G6" s="19"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="22" t="n">
@@ -515,15 +483,9 @@
         <x:v>FAIR data</x:v>
       </x:c>
       <x:c r="F7" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>Vrije Universiteit Amsterdam</x:v>
       </x:c>
       <x:c r="G7" s="19" t="str">
-        <x:v>How to make training scalable?</x:v>
-      </x:c>
-      <x:c r="H7" s="19" t="str">
-        <x:v>Vrije Universiteit Amsterdam</x:v>
-      </x:c>
-      <x:c r="I7" s="19" t="str">
         <x:v>https://rdm.vu.nl/guides/data-lifecycle.html</x:v>
       </x:c>
     </x:row>
@@ -544,13 +506,9 @@
         <x:v>Software Development</x:v>
       </x:c>
       <x:c r="F8" s="19" t="str">
-        <x:v>Best Practice</x:v>
-      </x:c>
-      <x:c r="G8" s="19"/>
-      <x:c r="H8" s="19" t="str">
         <x:v>Utrecht University</x:v>
       </x:c>
-      <x:c r="I8" s="19" t="str">
+      <x:c r="G8" s="19" t="str">
         <x:v>https://cdh.uu.nl/2026/02/13/boost-your-coding-skills-at-the-research-software-summer-school-2026/</x:v>
       </x:c>
     </x:row>
@@ -571,13 +529,9 @@
         <x:v>Digital capacity building</x:v>
       </x:c>
       <x:c r="F9" s="19" t="str">
-        <x:v>Best Practice</x:v>
-      </x:c>
-      <x:c r="G9" s="19"/>
-      <x:c r="H9" s="19" t="str">
         <x:v>Delft University of Technology</x:v>
       </x:c>
-      <x:c r="I9" s="19" t="str">
+      <x:c r="G9" s="19" t="str">
         <x:v>https://tdcc.nl/nes/projects/building-digital-skills-training-and-lesson-development-capacity-in-the-netherlands-nes-domain/</x:v>
       </x:c>
     </x:row>
@@ -598,15 +552,9 @@
         <x:v>7 areas: RDM/OS/FAIR, RSM, legal/ethical, policy &amp; governance, training, transversal, data infrastructure</x:v>
       </x:c>
       <x:c r="F10" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>Delft University of Technology</x:v>
       </x:c>
       <x:c r="G10" s="19" t="str">
-        <x:v>Different training providers have different frequencies, quality, content, governane &amp; admin workflows which need to be algned to some extent for a national training programme</x:v>
-      </x:c>
-      <x:c r="H10" s="19" t="str">
-        <x:v>Delft University of Technology</x:v>
-      </x:c>
-      <x:c r="I10" s="19" t="str">
         <x:v>https://researchdata.nl/</x:v>
       </x:c>
     </x:row>
@@ -627,15 +575,9 @@
         <x:v>Programming</x:v>
       </x:c>
       <x:c r="F11" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>University of Groningen</x:v>
       </x:c>
       <x:c r="G11" s="19" t="str">
-        <x:v>Advertising etc.</x:v>
-      </x:c>
-      <x:c r="H11" s="19" t="str">
-        <x:v>University of Groningen</x:v>
-      </x:c>
-      <x:c r="I11" s="19" t="str">
         <x:v>https://www.rug.nl/digital-competence-centre/calendar/2026/code-cafe-26-02-2026?lang=en</x:v>
       </x:c>
     </x:row>
@@ -656,15 +598,9 @@
         <x:v>Brining AI into research life</x:v>
       </x:c>
       <x:c r="F12" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>University of Twente</x:v>
       </x:c>
       <x:c r="G12" s="19" t="str">
-        <x:v>Find balance between use of AI in Research and working with data</x:v>
-      </x:c>
-      <x:c r="H12" s="19" t="str">
-        <x:v>University of Twente</x:v>
-      </x:c>
-      <x:c r="I12" s="19" t="str">
         <x:v>https://www.utwente.nl/en/ctd/courses/1000227/data-management-bootcamp/</x:v>
       </x:c>
     </x:row>
@@ -685,15 +621,9 @@
         <x:v>Cloud-native research, energy awareness/efficiency, HPC&lt; research software development best practices, RDM</x:v>
       </x:c>
       <x:c r="F13" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>University of Twente</x:v>
       </x:c>
       <x:c r="G13" s="19" t="str">
-        <x:v>Visibility &amp; uptake of outputs (tools, guidelines, etc.); Have training participants (given that they have AI support now)</x:v>
-      </x:c>
-      <x:c r="H13" s="19" t="str">
-        <x:v>University of Twente</x:v>
-      </x:c>
-      <x:c r="I13" s="19" t="str">
         <x:v>https://tdcc.nl/nes/projects/cloud-nes-facilitating-cloud-native-data-access-and-processing-for-nes/</x:v>
       </x:c>
     </x:row>
@@ -712,15 +642,9 @@
         <x:v>Information literacy, research skills, literature research</x:v>
       </x:c>
       <x:c r="F14" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>Saxion University of Applied Sciences</x:v>
       </x:c>
       <x:c r="G14" s="19" t="str">
-        <x:v>Communicating with Researchers - how do I get in touch with them? How can I get them to follow workshops? They say they never have time</x:v>
-      </x:c>
-      <x:c r="H14" s="19" t="str">
-        <x:v>Saxion University of Applied Sciences</x:v>
-      </x:c>
-      <x:c r="I14" s="19" t="str">
         <x:v>https://saxionbibliotheek.nl/</x:v>
       </x:c>
     </x:row>
@@ -739,15 +663,9 @@
       </x:c>
       <x:c r="E15" s="19"/>
       <x:c r="F15" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>TDCC-NES Project</x:v>
       </x:c>
       <x:c r="G15" s="19" t="str">
-        <x:v>increasing need for training; scarce human capacity</x:v>
-      </x:c>
-      <x:c r="H15" s="19" t="str">
-        <x:v>TDCC-NES Project</x:v>
-      </x:c>
-      <x:c r="I15" s="19" t="str">
         <x:v>https://tdcc.nl/nes/projects/</x:v>
       </x:c>
     </x:row>
@@ -768,15 +686,9 @@
         <x:v>Containers/Kubenetes</x:v>
       </x:c>
       <x:c r="F16" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>Wageningen University &amp; Research</x:v>
       </x:c>
       <x:c r="G16" s="19" t="str">
-        <x:v>Not enough time / trainers on advanced topics</x:v>
-      </x:c>
-      <x:c r="H16" s="19" t="str">
-        <x:v>Wageningen University &amp; Research</x:v>
-      </x:c>
-      <x:c r="I16" s="19" t="str">
         <x:v>https://wiki.anunna.wur.nl/Workshops</x:v>
       </x:c>
     </x:row>
@@ -797,15 +709,9 @@
         <x:v>Create community of FAIR trainers, create OER materials</x:v>
       </x:c>
       <x:c r="F17" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>Health-RI</x:v>
       </x:c>
       <x:c r="G17" s="19" t="str">
-        <x:v>TDCC-LSH project funded 1 april 2025-31 march 2027. Idea to set up training hubs for FAIR, exchange</x:v>
-      </x:c>
-      <x:c r="H17" s="19" t="str">
-        <x:v>Health-RI</x:v>
-      </x:c>
-      <x:c r="I17" s="19" t="str">
         <x:v>https://learn-fair.nl/</x:v>
       </x:c>
     </x:row>
@@ -826,13 +732,9 @@
         <x:v>Research Software Management</x:v>
       </x:c>
       <x:c r="F18" s="19" t="str">
-        <x:v>Best Practie</x:v>
-      </x:c>
-      <x:c r="G18" s="19"/>
-      <x:c r="H18" s="19" t="str">
         <x:v>Vrije Universiteit Amsterdam</x:v>
       </x:c>
-      <x:c r="I18" s="19" t="str">
+      <x:c r="G18" s="19" t="str">
         <x:v>https://ubvu.github.io/bytes-and-bites/</x:v>
       </x:c>
     </x:row>
@@ -853,15 +755,9 @@
         <x:v>Basic programming skills</x:v>
       </x:c>
       <x:c r="F19" s="19" t="str">
-        <x:v>Best Practice</x:v>
-      </x:c>
-      <x:c r="G19" s="19" t="str">
-        <x:v>Regional collaboration to organize software carpentries</x:v>
-      </x:c>
-      <x:c r="H19" s="19" t="str">
         <x:v>Amsterdam Universities, University Medical Centers &amp; University of Applied Sciences</x:v>
       </x:c>
-      <x:c r="I19" s="19"/>
+      <x:c r="G19" s="19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="22" t="n">
@@ -880,13 +776,9 @@
         <x:v>Research software training network</x:v>
       </x:c>
       <x:c r="F20" s="19" t="str">
-        <x:v>Best Practice</x:v>
-      </x:c>
-      <x:c r="G20" s="19"/>
-      <x:c r="H20" s="19" t="str">
         <x:v>Netherlands eScience Center</x:v>
       </x:c>
-      <x:c r="I20" s="19" t="str">
+      <x:c r="G20" s="19" t="str">
         <x:v>https://researchsoftwaretraining.nl/</x:v>
       </x:c>
     </x:row>
@@ -907,21 +799,15 @@
         <x:v>Large Scale Computing</x:v>
       </x:c>
       <x:c r="F21" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>Utrecht University</x:v>
       </x:c>
       <x:c r="G21" s="19" t="str">
-        <x:v>Maintaining/sustainability, Keeping track with technological developments</x:v>
-      </x:c>
-      <x:c r="H21" s="19" t="str">
-        <x:v>Utrecht University</x:v>
-      </x:c>
-      <x:c r="I21" s="19" t="str">
         <x:v>https://bookings.uu.nl/event/4346947</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="19" t="str">
         <x:v>Digital Lab</x:v>
@@ -934,21 +820,15 @@
       </x:c>
       <x:c r="E22" s="19"/>
       <x:c r="F22" s="19" t="str">
-        <x:v>Challenge/Best Practice</x:v>
+        <x:v>Leiden University</x:v>
       </x:c>
       <x:c r="G22" s="19" t="str">
-        <x:v>Fdigital skills within the humanities / support, peers and tools in one place</x:v>
-      </x:c>
-      <x:c r="H22" s="19" t="str">
-        <x:v>Leiden University</x:v>
-      </x:c>
-      <x:c r="I22" s="19" t="str">
         <x:v>https://www.universiteitleiden.nl/en/humanities/centre-for-digital-humanities/hub/digital-lab</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="19" t="str">
         <x:v>Coding Cafe Tu/e Built environment + Coding Cafe Leiden UMC</x:v>
@@ -963,21 +843,15 @@
         <x:v>Research Software Community Building</x:v>
       </x:c>
       <x:c r="F23" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>Eindhoven University of Technology</x:v>
       </x:c>
       <x:c r="G23" s="19" t="str">
-        <x:v>Find topics, speakers, lack of funding, repetitive communication tasks</x:v>
-      </x:c>
-      <x:c r="H23" s="19" t="str">
-        <x:v>Eindhoven University of Technology</x:v>
-      </x:c>
-      <x:c r="I23" s="19" t="str">
         <x:v>https://www.becodingcafe.com/</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="19" t="str">
         <x:v>High-Performance Computing Spring/Autumn Schools</x:v>
@@ -992,21 +866,15 @@
         <x:v>HPC for SIMS &amp; AI</x:v>
       </x:c>
       <x:c r="F24" s="19" t="str">
-        <x:v>Challenge </x:v>
+        <x:v>Eindhoven University of Technology</x:v>
       </x:c>
       <x:c r="G24" s="19" t="str">
-        <x:v>"Tension" when collab w/ industry</x:v>
-      </x:c>
-      <x:c r="H24" s="19" t="str">
-        <x:v>Eindhoven University of Technology</x:v>
-      </x:c>
-      <x:c r="I24" s="19" t="str">
         <x:v>https://supercomputing.tue.nl/hpc-school/</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="19" t="str">
         <x:v>Databites</x:v>
@@ -1020,18 +888,16 @@
       <x:c r="E25" s="19" t="str">
         <x:v>Short topical meetings on RDM-practices when necessary</x:v>
       </x:c>
-      <x:c r="F25" s="19"/>
-      <x:c r="G25" s="19"/>
-      <x:c r="H25" s="19" t="str">
+      <x:c r="F25" s="19" t="str">
         <x:v>Eindhoven University of Technology</x:v>
       </x:c>
-      <x:c r="I25" s="19" t="str">
+      <x:c r="G25" s="19" t="str">
         <x:v>https://rdm.tue.nl/docs/learning-resources/data-bites/</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="19" t="str">
         <x:v>Data in Humanities and Social Sciences</x:v>
@@ -1046,21 +912,15 @@
         <x:v>Managing + Sharing Sensitive Data in the Humanities</x:v>
       </x:c>
       <x:c r="F26" s="19" t="str">
-        <x:v>Challenge/Best Practice</x:v>
+        <x:v>DANS-KNAW</x:v>
       </x:c>
       <x:c r="G26" s="19" t="str">
-        <x:v>Sensitive Data/Technical + theoretical solutions to deal with these challenges</x:v>
-      </x:c>
-      <x:c r="H26" s="19" t="str">
-        <x:v>DANS-KNAW</x:v>
-      </x:c>
-      <x:c r="I26" s="19" t="str">
         <x:v>https://dans.knaw.nl/en/training/open-fair-data/</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="19" t="str">
         <x:v>HPC School</x:v>
@@ -1075,19 +935,15 @@
         <x:v>HPC School</x:v>
       </x:c>
       <x:c r="F27" s="19" t="str">
-        <x:v>Best Practice</x:v>
-      </x:c>
-      <x:c r="G27" s="19"/>
-      <x:c r="H27" s="19" t="str">
         <x:v>Eindhoven University of Technology</x:v>
       </x:c>
-      <x:c r="I27" s="19" t="str">
+      <x:c r="G27" s="19" t="str">
         <x:v>https://supercomputing.tue.nl/hpc-school/</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="19" t="str">
         <x:v>JASP Training</x:v>
@@ -1102,19 +958,13 @@
         <x:v>Open Source Statistics</x:v>
       </x:c>
       <x:c r="F28" s="19" t="str">
-        <x:v>Challenge</x:v>
-      </x:c>
-      <x:c r="G28" s="19" t="str">
-        <x:v>How to move towards open source statistics in an environment where legacy software (i.e. SPSS) has always been very strongly embedded in the curriculum</x:v>
-      </x:c>
-      <x:c r="H28" s="19" t="str">
         <x:v>Erasmus University Rotterdam</x:v>
       </x:c>
-      <x:c r="I28" s="19"/>
+      <x:c r="G28" s="19"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="19" t="str">
         <x:v>RS Training Modules</x:v>
@@ -1129,19 +979,15 @@
         <x:v>Research Software Training Modules</x:v>
       </x:c>
       <x:c r="F29" s="19" t="str">
-        <x:v>Best Practice</x:v>
-      </x:c>
-      <x:c r="G29" s="19"/>
-      <x:c r="H29" s="19" t="str">
         <x:v>Delft University of Technology</x:v>
       </x:c>
-      <x:c r="I29" s="19" t="str">
+      <x:c r="G29" s="19" t="str">
         <x:v>https://www.tudelft.nl/library/data-management/trainingen/trainingen-voor-onderzoekers-en</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="19" t="str">
         <x:v>The Plant</x:v>
@@ -1154,21 +1000,15 @@
       </x:c>
       <x:c r="E30" s="19"/>
       <x:c r="F30" s="19" t="str">
-        <x:v>Best Practice</x:v>
+        <x:v>Maastricht University</x:v>
       </x:c>
       <x:c r="G30" s="19" t="str">
-        <x:v>Playground laboratory for new technologies</x:v>
-      </x:c>
-      <x:c r="H30" s="19" t="str">
-        <x:v>Maastricht University</x:v>
-      </x:c>
-      <x:c r="I30" s="19" t="str">
         <x:v>https://theplant.maastrichtuniversity.nl/workshops/</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="19" t="str">
         <x:v>W.I.P. RDM workshops</x:v>
@@ -1183,21 +1023,15 @@
         <x:v>Research Data Management + Tools</x:v>
       </x:c>
       <x:c r="F31" s="19" t="str">
-        <x:v>Challenge/Best Practice</x:v>
+        <x:v>Zuyd University of Applied Sciences</x:v>
       </x:c>
       <x:c r="G31" s="19" t="str">
-        <x:v>Gathering researchers/ Open to tops and tricks</x:v>
-      </x:c>
-      <x:c r="H31" s="19" t="str">
-        <x:v>Zuyd University of Applied Sciences</x:v>
-      </x:c>
-      <x:c r="I31" s="19" t="str">
         <x:v>https://bibliotheek.zuyd.nl/en/practice-oriented-research/team-research-support</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="19" t="str">
         <x:v>Health-RI e-learning: onboarding for data stewards in medical research</x:v>
@@ -1212,21 +1046,15 @@
         <x:v>See above</x:v>
       </x:c>
       <x:c r="F32" s="19" t="str">
-        <x:v>Challenge</x:v>
+        <x:v>Amsterdam UMC</x:v>
       </x:c>
       <x:c r="G32" s="19" t="str">
-        <x:v>Difference per datasteward how different knowledge and digital skills are balanced/needed</x:v>
-      </x:c>
-      <x:c r="H32" s="19" t="str">
-        <x:v>Amsterdam UMC</x:v>
-      </x:c>
-      <x:c r="I32" s="19" t="str">
         <x:v>https://vedran-kasalica.github.io/FAIR_training_elearning/onboarding-overview</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="19" t="str">
         <x:v>DCC-PO </x:v>
@@ -1241,21 +1069,15 @@
         <x:v>Data &amp; Software Carpentries</x:v>
       </x:c>
       <x:c r="F33" s="19" t="str">
-        <x:v>Challenge/Best Practice</x:v>
+        <x:v>Saxion University of Applied Sciences</x:v>
       </x:c>
       <x:c r="G33" s="19" t="str">
-        <x:v>Researchers dont have enough time for training, its a challenge to travel / Smaller trainings focusing on R or Python, organized at different UASs</x:v>
-      </x:c>
-      <x:c r="H33" s="19" t="str">
-        <x:v>Saxion University of Applied Sciences</x:v>
-      </x:c>
-      <x:c r="I33" s="19" t="str">
         <x:v>https://dcc-po.nl/</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="23" t="n">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="20" t="str">
         <x:v>DCDC network</x:v>
@@ -1269,25 +1091,21 @@
       <x:c r="E34" s="20" t="str">
         <x:v>Data/Software/Open Science</x:v>
       </x:c>
-      <x:c r="F34" s="20"/>
+      <x:c r="F34" s="20" t="str">
+        <x:v>University of Aruba</x:v>
+      </x:c>
       <x:c r="G34" s="20" t="str">
-        <x:v>DCDC.network</x:v>
-      </x:c>
-      <x:c r="H34" s="20" t="str">
-        <x:v>University of Aruba</x:v>
-      </x:c>
-      <x:c r="I34" s="20" t="str">
         <x:v>https://dcdc.network/</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:I1"/>
-    <x:mergeCell ref="A2:I2"/>
+    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R246f3423c0554ef8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd082de51642f48fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>